--- a/public/templates/drug-upload-template.xlsx
+++ b/public/templates/drug-upload-template.xlsx
@@ -33,29 +33,84 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="8" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+      <color rgb="3A2A4D"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <color rgb="8A8A8A"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <i/>
+      <color rgb="B0B0B0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <i/>
+      <color rgb="B0B0B0"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill patternType="none">
+        <bgColor/>
+      </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF804A87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF804A87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFA6D9"/>
+        <bgColor/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -63,14 +118,56 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -402,274 +499,8740 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:U503"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="3" t="str">
         <v>약플로 약품 기초자료 등록 양식   ·   4행부터 입력하세요   ·   회색 예시 2줄은 지우고 사용하세요</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="4" t="str">
         <v>약품코드</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B2" s="4" t="str">
         <v>약품명</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C2" s="4" t="str">
         <v>보험코드</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D2" s="4" t="str">
         <v>품목기준코드</v>
       </c>
-      <c r="E2" t="str">
+      <c r="E2" s="4" t="str">
         <v>ATC번호</v>
       </c>
-      <c r="F2" t="str">
+      <c r="F2" s="4" t="str">
         <v>규격</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" s="4" t="str">
         <v>제형</v>
       </c>
-      <c r="H2" t="str">
+      <c r="H2" s="4" t="str">
         <v>포장</v>
       </c>
-      <c r="I2" t="str">
+      <c r="I2" s="4" t="str">
         <v>현재고</v>
       </c>
-      <c r="J2" t="str">
+      <c r="J2" s="4" t="str">
         <v>구입단가</v>
       </c>
-      <c r="K2" t="str">
+      <c r="K2" s="4" t="str">
         <v>보험약가</v>
       </c>
-      <c r="L2" t="str">
+      <c r="L2" s="4" t="str">
         <v>구분</v>
       </c>
-      <c r="M2" t="str">
+      <c r="M2" s="4" t="str">
         <v>상태</v>
       </c>
-      <c r="N2" t="str">
+      <c r="N2" s="4" t="str">
         <v>안전재고</v>
       </c>
-      <c r="O2" t="str">
+      <c r="O2" s="4" t="str">
         <v>최대재고</v>
       </c>
-      <c r="P2" t="str">
+      <c r="P2" s="4" t="str">
         <v>보관위치</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="Q2" s="4" t="str">
         <v>유효기한</v>
       </c>
-      <c r="R2" t="str">
+      <c r="R2" s="4" t="str">
         <v>LOT번호</v>
       </c>
-      <c r="S2" t="str">
+      <c r="S2" s="4" t="str">
         <v>비고</v>
       </c>
-      <c r="T2" t="str">
+      <c r="T2" s="5" t="str">
         <v>첨가제</v>
       </c>
-      <c r="U2" t="str">
+      <c r="U2" s="5" t="str">
         <v>복합/단일</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3" s="6" t="str">
         <v>필수 · 원내 약품코드</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B3" s="6" t="str">
         <v>필수 · 제품명</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C3" s="6" t="str">
         <v>권장 · 9자리 · 정확 매칭용</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D3" s="6" t="str">
         <v>권장 · 9자리 · 식약처 코드</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E3" s="6" t="str">
         <v>권장 · WHO 해부학적 분류코드</v>
       </c>
-      <c r="F3" t="str">
+      <c r="F3" s="6" t="str">
         <v>권장 · 입수 수량(숫자)</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G3" s="6" t="str">
         <v>권장 · 예: 정제·주사제</v>
       </c>
-      <c r="H3" t="str">
+      <c r="H3" s="6" t="str">
         <v>권장 · 예: 병·바이알</v>
       </c>
-      <c r="I3" t="str">
+      <c r="I3" s="6" t="str">
         <v>필수 · 현재 재고 수량</v>
       </c>
-      <c r="J3" t="str">
+      <c r="J3" s="6" t="str">
         <v>필수 · 1개당 매입가(원)</v>
       </c>
-      <c r="K3" t="str">
+      <c r="K3" s="6" t="str">
         <v>권장 · 심평원 상한가</v>
       </c>
-      <c r="L3" t="str">
+      <c r="L3" s="6" t="str">
         <v>선택 · 미입력 시 자동</v>
       </c>
-      <c r="M3" t="str">
+      <c r="M3" s="6" t="str">
         <v>선택 · 미입력 시 사용</v>
       </c>
-      <c r="N3" t="str">
+      <c r="N3" s="6" t="str">
         <v>권장 · 발주 기준점</v>
       </c>
-      <c r="O3" t="str">
+      <c r="O3" s="6" t="str">
         <v>권장 · 과잉 기준점</v>
       </c>
-      <c r="P3" t="str">
+      <c r="P3" s="6" t="str">
         <v>권장 · 예: A-3-2</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="Q3" s="6" t="str">
         <v>선택 · 대표 로트</v>
       </c>
-      <c r="R3" t="str">
+      <c r="R3" s="6" t="str">
         <v>선택 · 대표 로트번호</v>
       </c>
-      <c r="S3" t="str">
+      <c r="S3" s="6" t="str">
         <v>선택</v>
       </c>
-      <c r="T3" t="str">
+      <c r="T3" s="6" t="str">
         <v>선택 · 약가마스터 자동채움</v>
       </c>
-      <c r="U3" t="str">
+      <c r="U3" s="6" t="str">
         <v>선택 · 자동(단일제/복합제)</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4" s="7" t="str">
         <v>ABC01</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B4" s="8" t="str">
         <v>타이레놀정500mg</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C4" s="7" t="str">
         <v>645901230</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D4" s="7" t="str">
         <v>197000123</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E4" s="7" t="str">
         <v>N02BE01</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="8">
         <v>100</v>
       </c>
-      <c r="G4" t="str">
+      <c r="G4" s="8" t="str">
         <v>정제</v>
       </c>
-      <c r="H4" t="str">
+      <c r="H4" s="8" t="str">
         <v>병</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="8">
         <v>1200</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="8">
         <v>88</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="8">
         <v>88</v>
       </c>
-      <c r="L4" t="str">
+      <c r="L4" s="8" t="str">
         <v>경구제</v>
       </c>
-      <c r="M4" t="str">
+      <c r="M4" s="8" t="str">
         <v>사용</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="8">
         <v>300</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="8">
         <v>2000</v>
       </c>
-      <c r="P4" t="str">
+      <c r="P4" s="8" t="str">
         <v>A-3-2</v>
       </c>
-      <c r="Q4" t="str">
+      <c r="Q4" s="8" t="str">
         <v>2027-06-30</v>
       </c>
-      <c r="R4" t="str">
+      <c r="R4" s="7" t="str">
         <v>LOT2706</v>
       </c>
-      <c r="S4" t="str">
+      <c r="S4" s="8" t="str">
         <v>예시 — 삭제하세요</v>
       </c>
-      <c r="T4" t="str">
+      <c r="T4" s="8" t="str">
         <v>스테아르산마그네슘 등</v>
       </c>
-      <c r="U4" t="str">
+      <c r="U4" s="8" t="str">
         <v>단일제</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5" s="7" t="str">
         <v>INJ07</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B5" s="8" t="str">
         <v>세프트리악손주1g</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C5" s="7" t="str">
         <v>642203450</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D5" s="7" t="str">
         <v>640012345</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E5" s="7" t="str">
         <v>J01DD04</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="8">
         <v>1</v>
       </c>
-      <c r="G5" t="str">
+      <c r="G5" s="8" t="str">
         <v>주사제</v>
       </c>
-      <c r="H5" t="str">
+      <c r="H5" s="8" t="str">
         <v>바이알</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="8">
         <v>48</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="8">
         <v>3910</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="8">
         <v>3910</v>
       </c>
-      <c r="L5" t="str">
+      <c r="L5" s="8" t="str">
         <v>주사제</v>
       </c>
-      <c r="M5" t="str">
+      <c r="M5" s="8" t="str">
         <v>사용</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="8">
         <v>20</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="8">
         <v>120</v>
       </c>
-      <c r="P5" t="str">
+      <c r="P5" s="8" t="str">
         <v>냉장-B-1</v>
       </c>
-      <c r="Q5" t="str">
+      <c r="Q5" s="8" t="str">
         <v>2026-11-30</v>
       </c>
-      <c r="R5" t="str">
+      <c r="R5" s="7" t="str">
         <v>CTX2611</v>
       </c>
-      <c r="S5" t="str">
+      <c r="S5" s="8" t="str">
         <v>예시 — 삭제하세요</v>
       </c>
-      <c r="T5" t="str">
-        <v/>
-      </c>
-      <c r="U5" t="str">
+      <c r="T5" s="8" t="str">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="str">
         <v>단일제</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C6" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D6" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E6" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R6" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C7" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D7" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E7" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R7" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C8" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D8" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E8" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R8" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C9" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D9" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E9" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R9" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C10" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D10" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E10" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R10" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C11" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D11" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E11" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R11" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C12" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D12" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E12" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R12" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C13" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D13" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E13" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R13" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C14" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D14" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E14" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R14" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C15" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D15" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E15" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R15" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C16" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D16" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E16" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R16" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C17" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D17" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E17" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R17" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C18" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D18" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E18" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R18" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C19" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D19" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E19" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R19" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C20" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D20" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E20" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R20" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C21" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D21" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E21" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R21" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C22" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D22" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E22" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R22" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C23" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D23" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E23" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R23" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C24" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D24" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E24" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R24" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C25" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D25" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E25" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R25" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C26" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D26" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E26" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R26" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C27" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D27" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E27" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R27" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C28" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D28" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E28" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R28" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C29" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D29" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E29" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R29" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C30" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D30" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E30" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R30" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C31" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D31" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E31" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R31" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C32" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D32" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E32" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R32" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C33" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D33" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E33" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R33" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C34" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D34" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E34" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R34" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C35" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D35" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E35" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R35" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C36" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D36" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E36" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R36" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C37" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D37" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E37" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R37" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C38" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D38" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E38" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R38" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C39" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D39" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E39" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R39" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C40" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D40" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E40" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R40" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C41" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D41" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E41" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R41" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C42" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D42" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E42" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R42" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C43" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D43" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E43" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R43" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C44" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D44" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E44" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R44" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C45" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D45" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E45" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R45" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C46" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D46" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E46" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R46" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C47" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D47" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E47" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R47" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C48" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D48" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E48" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R48" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C49" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D49" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E49" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R49" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C50" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D50" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E50" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R50" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C51" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D51" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E51" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R51" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C52" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D52" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E52" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R52" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C53" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D53" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E53" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R53" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C54" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D54" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E54" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R54" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C55" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D55" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E55" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R55" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C56" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D56" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E56" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R56" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C57" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D57" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E57" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R57" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C58" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D58" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E58" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R58" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C59" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D59" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E59" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R59" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C60" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D60" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E60" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R60" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C61" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D61" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E61" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R61" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C62" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D62" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E62" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R62" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C63" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D63" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E63" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R63" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C64" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D64" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E64" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R64" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C65" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D65" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E65" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R65" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C66" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D66" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E66" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R66" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C67" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D67" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E67" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R67" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C68" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D68" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E68" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R68" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C69" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D69" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E69" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R69" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C70" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D70" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E70" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R70" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C71" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D71" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E71" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R71" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C72" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D72" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E72" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R72" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C73" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D73" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E73" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R73" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C74" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D74" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E74" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R74" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C75" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D75" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E75" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R75" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C76" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D76" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E76" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R76" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C77" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D77" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E77" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R77" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C78" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D78" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E78" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R78" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C79" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D79" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E79" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R79" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C80" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D80" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E80" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R80" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C81" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D81" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E81" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R81" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C82" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D82" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E82" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R82" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C83" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D83" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E83" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R83" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C84" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D84" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E84" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R84" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C85" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D85" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E85" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R85" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C86" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D86" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E86" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R86" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C87" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D87" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E87" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R87" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C88" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D88" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E88" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R88" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C89" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D89" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E89" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R89" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C90" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D90" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E90" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R90" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C91" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D91" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E91" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R91" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C92" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D92" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E92" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R92" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C93" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D93" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E93" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R93" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C94" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D94" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E94" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R94" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C95" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D95" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E95" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R95" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C96" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D96" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E96" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R96" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C97" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D97" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E97" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R97" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C98" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D98" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E98" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R98" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C99" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D99" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E99" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R99" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C100" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D100" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E100" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R100" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C101" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D101" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E101" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R101" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C102" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D102" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E102" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R102" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C103" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D103" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E103" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R103" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C104" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D104" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E104" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R104" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C105" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D105" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E105" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R105" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C106" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D106" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E106" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R106" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C107" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D107" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E107" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R107" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C108" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D108" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E108" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R108" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C109" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D109" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E109" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R109" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C110" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D110" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E110" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R110" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C111" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D111" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E111" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R111" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C112" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D112" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E112" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R112" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C113" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D113" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E113" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R113" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C114" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D114" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E114" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R114" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C115" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D115" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E115" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R115" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C116" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D116" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E116" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R116" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C117" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D117" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E117" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R117" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C118" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D118" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E118" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R118" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C119" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D119" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E119" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R119" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C120" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D120" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E120" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R120" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C121" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D121" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E121" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R121" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C122" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D122" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E122" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R122" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C123" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D123" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E123" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R123" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C124" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D124" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E124" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R124" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C125" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D125" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E125" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R125" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C126" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D126" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E126" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R126" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C127" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D127" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E127" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R127" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C128" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D128" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E128" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R128" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C129" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D129" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E129" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R129" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C130" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D130" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E130" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R130" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C131" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D131" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E131" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R131" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C132" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D132" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E132" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R132" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C133" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D133" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E133" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R133" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C134" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D134" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E134" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R134" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C135" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D135" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E135" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R135" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C136" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D136" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E136" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R136" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C137" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D137" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E137" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R137" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C138" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D138" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E138" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R138" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C139" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D139" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E139" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R139" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C140" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D140" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E140" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R140" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C141" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D141" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E141" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R141" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C142" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D142" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E142" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R142" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C143" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D143" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E143" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R143" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C144" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D144" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E144" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R144" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C145" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D145" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E145" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R145" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C146" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D146" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E146" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R146" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C147" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D147" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E147" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R147" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C148" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D148" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E148" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R148" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C149" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D149" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E149" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R149" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C150" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D150" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E150" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R150" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C151" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D151" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E151" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R151" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C152" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D152" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E152" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R152" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C153" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D153" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E153" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R153" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C154" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D154" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E154" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R154" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C155" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D155" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E155" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R155" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C156" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D156" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E156" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R156" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C157" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D157" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E157" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R157" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C158" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D158" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E158" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R158" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C159" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D159" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E159" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R159" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C160" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D160" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E160" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R160" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C161" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D161" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E161" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R161" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C162" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D162" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E162" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R162" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C163" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D163" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E163" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R163" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C164" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D164" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E164" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R164" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C165" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D165" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E165" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R165" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C166" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D166" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E166" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R166" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C167" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D167" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E167" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R167" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C168" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D168" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E168" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R168" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C169" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D169" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E169" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R169" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C170" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D170" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E170" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R170" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C171" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D171" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E171" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R171" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C172" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D172" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E172" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R172" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C173" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D173" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E173" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R173" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C174" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D174" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E174" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R174" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C175" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D175" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E175" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R175" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C176" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D176" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E176" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R176" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C177" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D177" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E177" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R177" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C178" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D178" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E178" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R178" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C179" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D179" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E179" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R179" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C180" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D180" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E180" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R180" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C181" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D181" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E181" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R181" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C182" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D182" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E182" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R182" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C183" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D183" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E183" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R183" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C184" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D184" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E184" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R184" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C185" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D185" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E185" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R185" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C186" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D186" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E186" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R186" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C187" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D187" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E187" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R187" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C188" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D188" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E188" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R188" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C189" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D189" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E189" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R189" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C190" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D190" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E190" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R190" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C191" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D191" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E191" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R191" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C192" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D192" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E192" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R192" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C193" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D193" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E193" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R193" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C194" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D194" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E194" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R194" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C195" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D195" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E195" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R195" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C196" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D196" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E196" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R196" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C197" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D197" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E197" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R197" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C198" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D198" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E198" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R198" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C199" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D199" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E199" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R199" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C200" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D200" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E200" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R200" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C201" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D201" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E201" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R201" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C202" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D202" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E202" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R202" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C203" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D203" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E203" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R203" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C204" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D204" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E204" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R204" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C205" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D205" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E205" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R205" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C206" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D206" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E206" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R206" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C207" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D207" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E207" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R207" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C208" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D208" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E208" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R208" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C209" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D209" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E209" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R209" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C210" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D210" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E210" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R210" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C211" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D211" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E211" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R211" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C212" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D212" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E212" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R212" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C213" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D213" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E213" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R213" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C214" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D214" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E214" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R214" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C215" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D215" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E215" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R215" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C216" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D216" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E216" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R216" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C217" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D217" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E217" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R217" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C218" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D218" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E218" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R218" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C219" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D219" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E219" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R219" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C220" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D220" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E220" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R220" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C221" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D221" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E221" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R221" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C222" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D222" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E222" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R222" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C223" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D223" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E223" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R223" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C224" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D224" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E224" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R224" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C225" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D225" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E225" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R225" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C226" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D226" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E226" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R226" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C227" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D227" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E227" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R227" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C228" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D228" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E228" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R228" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C229" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D229" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E229" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R229" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C230" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D230" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E230" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R230" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C231" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D231" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E231" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R231" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C232" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D232" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E232" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R232" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C233" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D233" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E233" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R233" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C234" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D234" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E234" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R234" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C235" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D235" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E235" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R235" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C236" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D236" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E236" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R236" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C237" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D237" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E237" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R237" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C238" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D238" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E238" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R238" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C239" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D239" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E239" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R239" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C240" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D240" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E240" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R240" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C241" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D241" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E241" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R241" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C242" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D242" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E242" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R242" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C243" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D243" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E243" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R243" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C244" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D244" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E244" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R244" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C245" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D245" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E245" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R245" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C246" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D246" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E246" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R246" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C247" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D247" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E247" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R247" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C248" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D248" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E248" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R248" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C249" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D249" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E249" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R249" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C250" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D250" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E250" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R250" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C251" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D251" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E251" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R251" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C252" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D252" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E252" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R252" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C253" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D253" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E253" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R253" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C254" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D254" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E254" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R254" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C255" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D255" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E255" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R255" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C256" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D256" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E256" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R256" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C257" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D257" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E257" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R257" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C258" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D258" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E258" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R258" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C259" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D259" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E259" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R259" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C260" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D260" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E260" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R260" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C261" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D261" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E261" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R261" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C262" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D262" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E262" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R262" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C263" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D263" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E263" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R263" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C264" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D264" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E264" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R264" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C265" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D265" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E265" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R265" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C266" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D266" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E266" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R266" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C267" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D267" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E267" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R267" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C268" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D268" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E268" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R268" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C269" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D269" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E269" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R269" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C270" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D270" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E270" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R270" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C271" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D271" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E271" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R271" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C272" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D272" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E272" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R272" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C273" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D273" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E273" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R273" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C274" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D274" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E274" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R274" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C275" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D275" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E275" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R275" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C276" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D276" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E276" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R276" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C277" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D277" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E277" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R277" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C278" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D278" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E278" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R278" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C279" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D279" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E279" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R279" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C280" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D280" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E280" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R280" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C281" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D281" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E281" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R281" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C282" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D282" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E282" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R282" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C283" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D283" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E283" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R283" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C284" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D284" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E284" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R284" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C285" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D285" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E285" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R285" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C286" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D286" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E286" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R286" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C287" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D287" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E287" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R287" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C288" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D288" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E288" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R288" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C289" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D289" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E289" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R289" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C290" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D290" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E290" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R290" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C291" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D291" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E291" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R291" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C292" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D292" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E292" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R292" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C293" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D293" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E293" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R293" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C294" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D294" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E294" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R294" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C295" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D295" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E295" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R295" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C296" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D296" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E296" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R296" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C297" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D297" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E297" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R297" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C298" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D298" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E298" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R298" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C299" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D299" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E299" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R299" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C300" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D300" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E300" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R300" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C301" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D301" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E301" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R301" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C302" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D302" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E302" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R302" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C303" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D303" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E303" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R303" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C304" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D304" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E304" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R304" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C305" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D305" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E305" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R305" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C306" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D306" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E306" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R306" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C307" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D307" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E307" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R307" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C308" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D308" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E308" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R308" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C309" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D309" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E309" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R309" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C310" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D310" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E310" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R310" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C311" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D311" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E311" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R311" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C312" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D312" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E312" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R312" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C313" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D313" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E313" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R313" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C314" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D314" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E314" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R314" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C315" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D315" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E315" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R315" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C316" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D316" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E316" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R316" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C317" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D317" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E317" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R317" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C318" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D318" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E318" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R318" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C319" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D319" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E319" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R319" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C320" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D320" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E320" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R320" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C321" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D321" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E321" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R321" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C322" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D322" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E322" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R322" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C323" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D323" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E323" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R323" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C324" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D324" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E324" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R324" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C325" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D325" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E325" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R325" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C326" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D326" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E326" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R326" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C327" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D327" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E327" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R327" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C328" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D328" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E328" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R328" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C329" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D329" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E329" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R329" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C330" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D330" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E330" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R330" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C331" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D331" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E331" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R331" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C332" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D332" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E332" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R332" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C333" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D333" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E333" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R333" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C334" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D334" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E334" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R334" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C335" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D335" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E335" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R335" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C336" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D336" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E336" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R336" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C337" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D337" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E337" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R337" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C338" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D338" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E338" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R338" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C339" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D339" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E339" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R339" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C340" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D340" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E340" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R340" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C341" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D341" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E341" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R341" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C342" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D342" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E342" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R342" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C343" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D343" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E343" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R343" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C344" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D344" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E344" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R344" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C345" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D345" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E345" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R345" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C346" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D346" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E346" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R346" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C347" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D347" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E347" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R347" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C348" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D348" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E348" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R348" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C349" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D349" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E349" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R349" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C350" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D350" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E350" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R350" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C351" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D351" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E351" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R351" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C352" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D352" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E352" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R352" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C353" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D353" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E353" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R353" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C354" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D354" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E354" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R354" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C355" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D355" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E355" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R355" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C356" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D356" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E356" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R356" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C357" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D357" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E357" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R357" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C358" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D358" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E358" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R358" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C359" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D359" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E359" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R359" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C360" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D360" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E360" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R360" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C361" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D361" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E361" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R361" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C362" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D362" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E362" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R362" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C363" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D363" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E363" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R363" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C364" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D364" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E364" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R364" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C365" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D365" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E365" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R365" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C366" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D366" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E366" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R366" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C367" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D367" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E367" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R367" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C368" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D368" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E368" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R368" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C369" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D369" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E369" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R369" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C370" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D370" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E370" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R370" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C371" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D371" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E371" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R371" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C372" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D372" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E372" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R372" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C373" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D373" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E373" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R373" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C374" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D374" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E374" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R374" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C375" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D375" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E375" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R375" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C376" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D376" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E376" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R376" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C377" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D377" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E377" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R377" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C378" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D378" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E378" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R378" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C379" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D379" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E379" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R379" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C380" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D380" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E380" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R380" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C381" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D381" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E381" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R381" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C382" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D382" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E382" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R382" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C383" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D383" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E383" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R383" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C384" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D384" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E384" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R384" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C385" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D385" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E385" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R385" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C386" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D386" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E386" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R386" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C387" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D387" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E387" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R387" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C388" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D388" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E388" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R388" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C389" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D389" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E389" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R389" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C390" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D390" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E390" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R390" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C391" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D391" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E391" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R391" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C392" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D392" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E392" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R392" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C393" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D393" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E393" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R393" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C394" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D394" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E394" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R394" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C395" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D395" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E395" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R395" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C396" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D396" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E396" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R396" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C397" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D397" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E397" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R397" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C398" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D398" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E398" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R398" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C399" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D399" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E399" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R399" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C400" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D400" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E400" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R400" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C401" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D401" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E401" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R401" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C402" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D402" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E402" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R402" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C403" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D403" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E403" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R403" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C404" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D404" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E404" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R404" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C405" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D405" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E405" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R405" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C406" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D406" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E406" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R406" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C407" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D407" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E407" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R407" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C408" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D408" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E408" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R408" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C409" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D409" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E409" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R409" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C410" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D410" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E410" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R410" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C411" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D411" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E411" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R411" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C412" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D412" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E412" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R412" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C413" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D413" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E413" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R413" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C414" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D414" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E414" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R414" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C415" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D415" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E415" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R415" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C416" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D416" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E416" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R416" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C417" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D417" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E417" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R417" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C418" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D418" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E418" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R418" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C419" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D419" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E419" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R419" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C420" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D420" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E420" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R420" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C421" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D421" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E421" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R421" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C422" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D422" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E422" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R422" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C423" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D423" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E423" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R423" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C424" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D424" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E424" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R424" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C425" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D425" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E425" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R425" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C426" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D426" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E426" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R426" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C427" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D427" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E427" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R427" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C428" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D428" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E428" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R428" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C429" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D429" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E429" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R429" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C430" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D430" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E430" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R430" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C431" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D431" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E431" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R431" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C432" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D432" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E432" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R432" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C433" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D433" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E433" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R433" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C434" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D434" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E434" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R434" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C435" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D435" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E435" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R435" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C436" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D436" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E436" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R436" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C437" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D437" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E437" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R437" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C438" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D438" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E438" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R438" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C439" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D439" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E439" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R439" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C440" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D440" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E440" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R440" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C441" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D441" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E441" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R441" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C442" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D442" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E442" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R442" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C443" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D443" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E443" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R443" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C444" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D444" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E444" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R444" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C445" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D445" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E445" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R445" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C446" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D446" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E446" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R446" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C447" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D447" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E447" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R447" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C448" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D448" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E448" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R448" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C449" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D449" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E449" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R449" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C450" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D450" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E450" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R450" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C451" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D451" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E451" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R451" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C452" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D452" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E452" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R452" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C453" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D453" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E453" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R453" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C454" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D454" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E454" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R454" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C455" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D455" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E455" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R455" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C456" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D456" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E456" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R456" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C457" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D457" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E457" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R457" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C458" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D458" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E458" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R458" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C459" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D459" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E459" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R459" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C460" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D460" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E460" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R460" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C461" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D461" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E461" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R461" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C462" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D462" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E462" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R462" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C463" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D463" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E463" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R463" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C464" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D464" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E464" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R464" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C465" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D465" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E465" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R465" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C466" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D466" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E466" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R466" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C467" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D467" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E467" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R467" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C468" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D468" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E468" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R468" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C469" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D469" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E469" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R469" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C470" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D470" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E470" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R470" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C471" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D471" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E471" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R471" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C472" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D472" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E472" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R472" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C473" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D473" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E473" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R473" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C474" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D474" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E474" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R474" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C475" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D475" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E475" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R475" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C476" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D476" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E476" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R476" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C477" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D477" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E477" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R477" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C478" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D478" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E478" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R478" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C479" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D479" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E479" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R479" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C480" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D480" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E480" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R480" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C481" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D481" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E481" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R481" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C482" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D482" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E482" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R482" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C483" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D483" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E483" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R483" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C484" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D484" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E484" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R484" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C485" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D485" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E485" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R485" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C486" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D486" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E486" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R486" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C487" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D487" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E487" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R487" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C488" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D488" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E488" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R488" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C489" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D489" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E489" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R489" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C490" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D490" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E490" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R490" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C491" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D491" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E491" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R491" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C492" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D492" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E492" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R492" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C493" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D493" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E493" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R493" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C494" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D494" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E494" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R494" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C495" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D495" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E495" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R495" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C496" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D496" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E496" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R496" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C497" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D497" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E497" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R497" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C498" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D498" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E498" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R498" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C499" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D499" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E499" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R499" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C500" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D500" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E500" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R500" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C501" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D501" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E501" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R501" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C502" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D502" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E502" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R502" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="9" t="str">
+        <v/>
+      </c>
+      <c r="C503" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D503" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E503" s="9" t="str">
+        <v/>
+      </c>
+      <c r="R503" s="9" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A1:U1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -683,358 +9246,358 @@
   <dimension ref="A1:E25"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" s="2" t="str">
         <v>컬럼별 입력 안내</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2" s="2" t="str">
         <v>컬럼</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B2" s="2" t="str">
         <v>필수 여부</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C2" s="2" t="str">
         <v>형식</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D2" s="2" t="str">
         <v>설명</v>
       </c>
-      <c r="E2" t="str">
+      <c r="E2" s="2" t="str">
         <v>미입력 시</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3" s="2" t="str">
         <v>약품코드</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B3" s="2" t="str">
         <v>필수</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C3" s="2" t="str">
         <v>문자</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D3" s="2" t="str">
         <v>병원에서 쓰는 원내 코드</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E3" s="2" t="str">
         <v>등록 실패</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4" s="2" t="str">
         <v>약품명</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B4" s="2" t="str">
         <v>필수</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C4" s="2" t="str">
         <v>문자</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D4" s="2" t="str">
         <v>제품명. 보험코드가 있으면 이름이 조금 달라도 됩니다</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E4" s="2" t="str">
         <v>등록 실패</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5" s="2" t="str">
         <v>보험코드</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B5" s="2" t="str">
         <v>권장</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C5" s="2" t="str">
         <v>9자리 숫자</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D5" s="2" t="str">
         <v>있으면 성분·ATC·보험약가가 정확히 자동 입력됩니다</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E5" s="2" t="str">
         <v>약품명으로 매칭</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
+      <c r="A6" s="2" t="str">
         <v>품목기준코드</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B6" s="2" t="str">
         <v>권장</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C6" s="2" t="str">
         <v>9자리 숫자</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D6" s="2" t="str">
         <v>식약처 품목기준코드. 보험코드가 있으면 자동 입력됩니다</v>
       </c>
-      <c r="E6" t="str">
+      <c r="E6" s="2" t="str">
         <v>공공DB에서 자동</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
+      <c r="A7" s="2" t="str">
         <v>ATC번호</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B7" s="2" t="str">
         <v>권장</v>
       </c>
-      <c r="C7" t="str">
+      <c r="C7" s="2" t="str">
         <v>영문+숫자</v>
       </c>
-      <c r="D7" t="str">
+      <c r="D7" s="2" t="str">
         <v>WHO 해부학적 분류코드(예: N02BE01). 보험코드가 있으면 자동</v>
       </c>
-      <c r="E7" t="str">
+      <c r="E7" s="2" t="str">
         <v>공공DB에서 자동</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
+      <c r="A8" s="2" t="str">
         <v>규격</v>
       </c>
-      <c r="B8" t="str">
+      <c r="B8" s="2" t="str">
         <v>권장</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C8" s="2" t="str">
         <v>숫자</v>
       </c>
-      <c r="D8" t="str">
+      <c r="D8" s="2" t="str">
         <v>한 포장당 입수 수량(예: 100정=100). 낱개면 1</v>
       </c>
-      <c r="E8" t="str">
+      <c r="E8" s="2" t="str">
         <v>빈 값 유지</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
+      <c r="A9" s="2" t="str">
         <v>제형</v>
       </c>
-      <c r="B9" t="str">
+      <c r="B9" s="2" t="str">
         <v>권장</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C9" s="2" t="str">
         <v>문자</v>
       </c>
-      <c r="D9" t="str">
+      <c r="D9" s="2" t="str">
         <v>예: 정제·캡슐·주사제·시럽·연고</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E9" s="2" t="str">
         <v>공공DB에서 자동</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
+      <c r="A10" s="2" t="str">
         <v>포장</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B10" s="2" t="str">
         <v>권장</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C10" s="2" t="str">
         <v>문자</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D10" s="2" t="str">
         <v>예: 병·PTP·바이알·튜브</v>
       </c>
-      <c r="E10" t="str">
+      <c r="E10" s="2" t="str">
         <v>공공DB에서 자동</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
+      <c r="A11" s="2" t="str">
         <v>현재고</v>
       </c>
-      <c r="B11" t="str">
+      <c r="B11" s="2" t="str">
         <v>필수</v>
       </c>
-      <c r="C11" t="str">
+      <c r="C11" s="2" t="str">
         <v>숫자</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D11" s="2" t="str">
         <v>등록 시점의 재고 수량. 0도 가능</v>
       </c>
-      <c r="E11" t="str">
+      <c r="E11" s="2" t="str">
         <v>0으로 처리</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
+      <c r="A12" s="2" t="str">
         <v>구입단가</v>
       </c>
-      <c r="B12" t="str">
+      <c r="B12" s="2" t="str">
         <v>필수</v>
       </c>
-      <c r="C12" t="str">
+      <c r="C12" s="2" t="str">
         <v>숫자</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D12" s="2" t="str">
         <v>1개당 매입가(원). 부가세 포함 여부는 병원 기준대로</v>
       </c>
-      <c r="E12" t="str">
+      <c r="E12" s="2" t="str">
         <v>재고금액이 0으로 표시됨</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
+      <c r="A13" s="2" t="str">
         <v>보험약가</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B13" s="2" t="str">
         <v>권장</v>
       </c>
-      <c r="C13" t="str">
+      <c r="C13" s="2" t="str">
         <v>숫자</v>
       </c>
-      <c r="D13" t="str">
+      <c r="D13" s="2" t="str">
         <v>심평원 상한가. 구입단가 기본값=보험약가, 비급여·할인 시 직접 입력</v>
       </c>
-      <c r="E13" t="str">
+      <c r="E13" s="2" t="str">
         <v>구입단가와 동일 처리</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
+      <c r="A14" s="2" t="str">
         <v>구분</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B14" s="2" t="str">
         <v>선택</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C14" s="2" t="str">
         <v>목록</v>
       </c>
-      <c r="D14" t="str">
+      <c r="D14" s="2" t="str">
         <v>경구제·주사제·외용제·영양제·수액제·의약외품</v>
       </c>
-      <c r="E14" t="str">
+      <c r="E14" s="2" t="str">
         <v>공공DB에서 자동 입력</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
+      <c r="A15" s="2" t="str">
         <v>상태</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B15" s="2" t="str">
         <v>선택</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C15" s="2" t="str">
         <v>목록</v>
       </c>
-      <c r="D15" t="str">
+      <c r="D15" s="2" t="str">
         <v>사용·중지·휴면</v>
       </c>
-      <c r="E15" t="str">
+      <c r="E15" s="2" t="str">
         <v>사용</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
+      <c r="A16" s="2" t="str">
         <v>안전재고</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B16" s="2" t="str">
         <v>권장</v>
       </c>
-      <c r="C16" t="str">
+      <c r="C16" s="2" t="str">
         <v>숫자</v>
       </c>
-      <c r="D16" t="str">
+      <c r="D16" s="2" t="str">
         <v>이 수량 아래로 내려가면 발주 알림</v>
       </c>
-      <c r="E16" t="str">
+      <c r="E16" s="2" t="str">
         <v>발주 알림 미작동</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
+      <c r="A17" s="2" t="str">
         <v>최대재고</v>
       </c>
-      <c r="B17" t="str">
+      <c r="B17" s="2" t="str">
         <v>권장</v>
       </c>
-      <c r="C17" t="str">
+      <c r="C17" s="2" t="str">
         <v>숫자</v>
       </c>
-      <c r="D17" t="str">
+      <c r="D17" s="2" t="str">
         <v>이 수량을 넘으면 과잉 표시</v>
       </c>
-      <c r="E17" t="str">
+      <c r="E17" s="2" t="str">
         <v>과잉 판정 미작동</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
+      <c r="A18" s="2" t="str">
         <v>보관위치</v>
       </c>
-      <c r="B18" t="str">
+      <c r="B18" s="2" t="str">
         <v>권장</v>
       </c>
-      <c r="C18" t="str">
+      <c r="C18" s="2" t="str">
         <v>문자</v>
       </c>
-      <c r="D18" t="str">
+      <c r="D18" s="2" t="str">
         <v>조제실 위치. 예: A-3-2, 냉장-B-1</v>
       </c>
-      <c r="E18" t="str">
+      <c r="E18" s="2" t="str">
         <v>위치 검색 불가</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
+      <c r="A19" s="2" t="str">
         <v>유효기한</v>
       </c>
-      <c r="B19" t="str">
+      <c r="B19" s="2" t="str">
         <v>선택</v>
       </c>
-      <c r="C19" t="str">
+      <c r="C19" s="2" t="str">
         <v>yyyy-mm-dd</v>
       </c>
-      <c r="D19" t="str">
+      <c r="D19" s="2" t="str">
         <v>대표 로트 기준</v>
       </c>
-      <c r="E19" t="str">
+      <c r="E19" s="2" t="str">
         <v>유효기한 알림 미작동</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
+      <c r="A20" s="2" t="str">
         <v>LOT번호</v>
       </c>
-      <c r="B20" t="str">
+      <c r="B20" s="2" t="str">
         <v>선택</v>
       </c>
-      <c r="C20" t="str">
+      <c r="C20" s="2" t="str">
         <v>문자</v>
       </c>
-      <c r="D20" t="str">
+      <c r="D20" s="2" t="str">
         <v>대표 로트번호</v>
       </c>
-      <c r="E20" t="str">
+      <c r="E20" s="2" t="str">
         <v>—</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
+      <c r="A21" s="2" t="str">
         <v>비고</v>
       </c>
-      <c r="B21" t="str">
+      <c r="B21" s="2" t="str">
         <v>선택</v>
       </c>
-      <c r="C21" t="str">
+      <c r="C21" s="2" t="str">
         <v>문자</v>
       </c>
-      <c r="D21" t="str">
+      <c r="D21" s="2" t="str">
         <v>메모</v>
       </c>
-      <c r="E21" t="str">
+      <c r="E21" s="2" t="str">
         <v>—</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
+      <c r="A23" s="2" t="str">
         <v>자동으로 채워지는 항목 (입력하지 않으셔도 됩니다)</v>
       </c>
     </row>
     <row r="24" xml:space="preserve">
-      <c r="A24" t="str" xml:space="preserve">
-        <v xml:space="preserve">성분명(한글·영문) · 약효분류 · 제조사 · 단위 · 급여구분 · 전문/일반 · 마약구분 · 복합/단일 · 첨가제 · 보관방법 · 효능_x000d_
+      <c r="A24" s="2" t="str" xml:space="preserve">
+        <v xml:space="preserve">성분명(한글·영문) · 약효분류 · 제조사 · 단위 · 급여구분 · 전문/일반 · 마약구분 · 복합/단일 · 첨가제 · 보관방법 · 효능_x000d__x000d_
 → 식약처·심평원 공공데이터에서 약플로가 자동으로 채웁니다. 품목기준코드·ATC번호·제형·규격·포장도 비워 두면 보험코드 기준으로 자동 입력됩니다.</v>
       </c>
     </row>
@@ -1056,171 +9619,171 @@
   <dimension ref="A1:C21"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" s="2" t="str">
         <v>허용값 목록 — 아래 값 외에는 등록되지 않습니다</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2" s="2" t="str">
         <v>항목</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B2" s="2" t="str">
         <v>허용값</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C2" s="2" t="str">
         <v>비고</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3" s="2" t="str">
         <v>구분</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B3" s="2" t="str">
         <v>경구제 · 주사제 · 외용제 · 영양제 · 수액제 · 의약외품</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C3" s="2" t="str">
         <v>미입력 시 공공DB에서 자동</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4" s="2" t="str">
         <v>상태</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B4" s="2" t="str">
         <v>사용 · 중지 · 휴면</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C4" s="2" t="str">
         <v>미입력 시 사용</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5" s="2" t="str">
         <v>제형(예시)</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B5" s="2" t="str">
         <v>정제 · 캡슐 · 주사제 · 시럽 · 연고 · 점안액</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C5" s="2" t="str">
         <v>자유 입력 — 예시 참고</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
+      <c r="A6" s="2" t="str">
         <v>포장(예시)</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B6" s="2" t="str">
         <v>병 · PTP · 바이알 · 앰플 · 튜브 · 포</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C6" s="2" t="str">
         <v>자유 입력 — 예시 참고</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
+      <c r="A7" s="2" t="str">
         <v>규격</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B7" s="2" t="str">
         <v>숫자만</v>
       </c>
-      <c r="C7" t="str">
+      <c r="C7" s="2" t="str">
         <v>한 포장당 입수 수량. 예: 100, 30, 1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
+      <c r="A8" s="2" t="str">
         <v>ATC번호</v>
       </c>
-      <c r="B8" t="str">
+      <c r="B8" s="2" t="str">
         <v>영문+숫자 7자리</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C8" s="2" t="str">
         <v>예: N02BE01 — 있으면 자동</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
+      <c r="A9" s="2" t="str">
         <v>품목기준코드</v>
       </c>
-      <c r="B9" t="str">
+      <c r="B9" s="2" t="str">
         <v>숫자 9자리</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C9" s="2" t="str">
         <v>식약처 코드 — 있으면 자동</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
+      <c r="A10" s="2" t="str">
         <v>구입단가</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B10" s="2" t="str">
         <v>숫자만</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C10" s="2" t="str">
         <v>1개당 매입가 — 모든 금액계산 기준</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
+      <c r="A11" s="2" t="str">
         <v>보험약가</v>
       </c>
-      <c r="B11" t="str">
+      <c r="B11" s="2" t="str">
         <v>숫자만</v>
       </c>
-      <c r="C11" t="str">
+      <c r="C11" s="2" t="str">
         <v>심평원 상한가. 구입단가 기본값=보험약가</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
+      <c r="A12" s="2" t="str">
         <v>급여구분</v>
       </c>
-      <c r="B12" t="str">
+      <c r="B12" s="2" t="str">
         <v>급여 · 비급여</v>
       </c>
-      <c r="C12" t="str">
+      <c r="C12" s="2" t="str">
         <v>자동 — 입력 불필요</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
+      <c r="A13" s="2" t="str">
         <v>마약구분</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B13" s="2" t="str">
         <v>일반 · 향정 · 마약 · 한외마약</v>
       </c>
-      <c r="C13" t="str">
+      <c r="C13" s="2" t="str">
         <v>자동 — 입력 불필요</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
+      <c r="A14" s="2" t="str">
         <v>보관방법</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B14" s="2" t="str">
         <v>실온 · 냉장 · 실온/차광 · 냉장/차광</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C14" s="2" t="str">
         <v>자동 — 입력 불필요</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
+      <c r="A15" s="2" t="str">
         <v>복합/단일</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B15" s="2" t="str">
         <v>단일제 · 복합제</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C15" s="2" t="str">
         <v>자동 — 입력 불필요</v>
       </c>
     </row>
     <row r="17" xml:space="preserve">
-      <c r="A17" t="str" xml:space="preserve">
-        <v xml:space="preserve">주의 사항_x000d_
-· 약품코드·보험코드·품목기준코드·ATC번호·LOT번호 열은 반드시 "텍스트" 서식으로 두세요._x000d_
-   숫자로 바꾸면 앞자리 0이 사라지거나 APR2 같은 코드가 날짜(2026-04-02)로 변환됩니다._x000d_
-   이 양식에는 이미 설정되어 있습니다._x000d_
-· 같은 약품코드를 두 번 넣으면 두 번째 행부터 오류로 처리됩니다._x000d_
+      <c r="A17" s="2" t="str" xml:space="preserve">
+        <v xml:space="preserve">주의 사항_x000d__x000d_
+· 약품코드·보험코드·품목기준코드·ATC번호·LOT번호 열은 반드시 "텍스트" 서식으로 두세요._x000d__x000d_
+   숫자로 바꾸면 앞자리 0이 사라지거나 APR2 같은 코드가 날짜(2026-04-02)로 변환됩니다._x000d__x000d_
+   이 양식에는 이미 설정되어 있습니다._x000d__x000d_
+· 같은 약품코드를 두 번 넣으면 두 번째 행부터 오류로 처리됩니다._x000d__x000d_
 · 빈 칸으로 두면 기존 값이 유지됩니다. 값을 지우려면 올바른 값으로 덮어써 주세요.</v>
       </c>
     </row>
